--- a/artfynd/S 1169-2022 artfynd.xlsx
+++ b/artfynd/S 1169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112438960</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370735</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782913</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370736</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370739</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1587,6 +1627,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101689678</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101689582</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94854832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2153,6 +2218,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94854828</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2278,6 +2348,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94854839</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2397,6 +2472,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95599900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2508,6 +2588,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68440885</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464131</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2730,6 +2820,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127732511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2846,6 +2941,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6995564</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2948,6 +3048,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464116</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3050,6 +3155,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127506222</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3162,6 +3272,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127732574</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3264,6 +3379,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464117</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3366,6 +3486,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127506494</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3477,6 +3602,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127732621</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3590,6 +3720,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127732660</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3691,6 +3826,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89029064</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3788,6 +3928,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89125231</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3889,6 +4034,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89028929</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3994,6 +4144,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89028107</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4099,6 +4254,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89028340</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4205,6 +4365,11 @@
           <t>Fågelinventering Vätternvatten 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130649925</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4307,6 +4472,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127506375</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4409,6 +4579,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127463968</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4507,6 +4682,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464081</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4613,6 +4793,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62086012</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4715,6 +4900,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197917</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4822,6 +5012,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57198819</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4943,6 +5138,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14434786</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5058,6 +5258,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110288415</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5189,6 +5394,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14434789</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5300,6 +5510,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58932468</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5397,6 +5612,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085983</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5514,6 +5734,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6977893</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5620,6 +5845,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62362043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5742,6 +5972,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6977891</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5853,6 +6088,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62536639</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5970,6 +6210,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6977894</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6072,6 +6317,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197819</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6178,6 +6428,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62891794</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6289,6 +6544,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62891796</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6390,6 +6650,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62891800</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6490,6 +6755,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66421155</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6603,6 +6873,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6977811</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6710,8 +6985,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118888775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>